--- a/survey_templates/045_organic_social_media_feedback--survey_templates.xlsx
+++ b/survey_templates/045_organic_social_media_feedback--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -983,7 +983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1198,17 +1198,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>post_type_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>entertainment</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Entertainment</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>entertainment</t>
+          <t>sports</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Entertainment</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>politics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Politics</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>politics</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Health</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>health</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>education</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Education</t>
         </is>
       </c>
     </row>
@@ -1322,27 +1322,10 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>education</t>
+          <t>travel</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>travel</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
         <is>
           <t>Travel</t>
         </is>
